--- a/data/trans_orig/P16A11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235941</t>
+          <t>236837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>287674</t>
+          <t>290662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406720</t>
+          <t>407120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>476771</t>
+          <t>473367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>660217</t>
+          <t>658047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745489</t>
+          <t>750417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>744049</t>
+          <t>741061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>795782</t>
+          <t>794886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>838342</t>
+          <t>841746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>908393</t>
+          <t>907993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1601346</t>
+          <t>1596418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1686618</t>
+          <t>1688788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90612</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130102</t>
+          <t>129839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>77207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>114366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175595</t>
+          <t>178130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232112</t>
+          <t>230013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1562292</t>
+          <t>1562555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1601782</t>
+          <t>1603097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1473111</t>
+          <t>1473307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1511722</t>
+          <t>1510466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3047955</t>
+          <t>3050054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3104472</t>
+          <t>3101937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58556</t>
+          <t>57399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55824</t>
+          <t>54944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90480</t>
+          <t>89318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492852</t>
+          <t>494009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520318</t>
+          <t>520467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>436862</t>
+          <t>437163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457529</t>
+          <t>457865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>937340</t>
+          <t>938502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971996</t>
+          <t>972876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379776</t>
+          <t>379184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>455223</t>
+          <t>449429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>520780</t>
+          <t>525033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>611006</t>
+          <t>608714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>920899</t>
+          <t>922669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1037997</t>
+          <t>1040186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2820302</t>
+          <t>2826096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2895749</t>
+          <t>2896341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2768191</t>
+          <t>2770483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2858417</t>
+          <t>2854164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5616725</t>
+          <t>5614536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5733823</t>
+          <t>5732053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309619</t>
+          <t>309200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>372422</t>
+          <t>369332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>532306</t>
+          <t>530048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>601593</t>
+          <t>608766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>855015</t>
+          <t>860139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>959426</t>
+          <t>955334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602221</t>
+          <t>605311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665024</t>
+          <t>665443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>732978</t>
+          <t>725805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>802265</t>
+          <t>804523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1349788</t>
+          <t>1353880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1454199</t>
+          <t>1449075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157892</t>
+          <t>159541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211609</t>
+          <t>211915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121917</t>
+          <t>122226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170269</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>292516</t>
+          <t>294638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>363611</t>
+          <t>363648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1748413</t>
+          <t>1748107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1802130</t>
+          <t>1800481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1580455</t>
+          <t>1579761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1628807</t>
+          <t>1628498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3347135</t>
+          <t>3347098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3418230</t>
+          <t>3416108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61906</t>
+          <t>61810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59572</t>
+          <t>59156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95208</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418426</t>
+          <t>418522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447557</t>
+          <t>447005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>413731</t>
+          <t>413548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>438891</t>
+          <t>437835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842778</t>
+          <t>839317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878414</t>
+          <t>878830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>522824</t>
+          <t>523474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>617190</t>
+          <t>616607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>694437</t>
+          <t>695863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>795031</t>
+          <t>792747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1243256</t>
+          <t>1245616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1374023</t>
+          <t>1375353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2797807</t>
+          <t>2798390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2892173</t>
+          <t>2891523</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2747918</t>
+          <t>2750202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2848512</t>
+          <t>2847086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5583923</t>
+          <t>5582593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5714690</t>
+          <t>5712330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206402</t>
+          <t>208891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254124</t>
+          <t>255953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>352382</t>
+          <t>350389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>417485</t>
+          <t>415752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>573973</t>
+          <t>572389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654766</t>
+          <t>655657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500223</t>
+          <t>498394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547945</t>
+          <t>545456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>577175</t>
+          <t>578908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642278</t>
+          <t>644271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1094241</t>
+          <t>1093350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1175034</t>
+          <t>1176618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194936</t>
+          <t>191947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>248421</t>
+          <t>250162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184277</t>
+          <t>183819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243650</t>
+          <t>243971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>392663</t>
+          <t>390290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>477935</t>
+          <t>471617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1827964</t>
+          <t>1826223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1881449</t>
+          <t>1884438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1744650</t>
+          <t>1744329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1804023</t>
+          <t>1804481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3586750</t>
+          <t>3593068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3672022</t>
+          <t>3674395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67309</t>
+          <t>66008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19010</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44162</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63986</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>101243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479577</t>
+          <t>480878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507811</t>
+          <t>508864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>504978</t>
+          <t>506514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530130</t>
+          <t>530041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>993948</t>
+          <t>994784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032041</t>
+          <t>1032083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>463584</t>
+          <t>465145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>546225</t>
+          <t>548358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>578283</t>
+          <t>583162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>676429</t>
+          <t>677769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1069920</t>
+          <t>1064886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1193793</t>
+          <t>1195175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2831393</t>
+          <t>2829260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2914034</t>
+          <t>2912473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2855671</t>
+          <t>2854331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2953817</t>
+          <t>2948938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5715925</t>
+          <t>5714543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5839798</t>
+          <t>5844832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169895</t>
+          <t>169128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>208187</t>
+          <t>207006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354314</t>
+          <t>353728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>397131</t>
+          <t>396821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534973</t>
+          <t>534272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>595940</t>
+          <t>594510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305755</t>
+          <t>306936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344047</t>
+          <t>344814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>355241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397748</t>
+          <t>398334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670064</t>
+          <t>671494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731031</t>
+          <t>731732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224060</t>
+          <t>227422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366470</t>
+          <t>366552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>271119</t>
+          <t>270184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>973320</t>
+          <t>949187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569675</t>
+          <t>575578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1427522</t>
+          <t>1322862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1922973</t>
+          <t>1922891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065383</t>
+          <t>2062021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1263825</t>
+          <t>1287958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1966026</t>
+          <t>1966961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3099066</t>
+          <t>3203726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3956913</t>
+          <t>3951010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92259</t>
+          <t>91355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128964</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>56113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79584</t>
+          <t>79856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154494</t>
+          <t>154252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196446</t>
+          <t>196529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517659</t>
+          <t>519117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>554364</t>
+          <t>555268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>580879</t>
+          <t>580607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604163</t>
+          <t>604350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1110640</t>
+          <t>1110557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1152592</t>
+          <t>1152834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>477531</t>
+          <t>469665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>679271</t>
+          <t>674367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>719005</t>
+          <t>720288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1357333</t>
+          <t>1420887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1314130</t>
+          <t>1317410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2071342</t>
+          <t>2100399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -6679,17 +6679,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2838039</t>
+          <t>2838040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2770737</t>
+          <t>2775642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2972477</t>
+          <t>2980344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2292337</t>
+          <t>2228783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2930665</t>
+          <t>2929382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5028336</t>
+          <t>4999279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5785548</t>
+          <t>5782268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450008</t>
+          <t>3450009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450008</t>
+          <t>3450009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450008</t>
+          <t>3450009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">

--- a/data/trans_orig/P16A11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236837</t>
+          <t>237290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290662</t>
+          <t>291134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407120</t>
+          <t>406156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>473367</t>
+          <t>475747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658047</t>
+          <t>662418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>750417</t>
+          <t>748764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>741061</t>
+          <t>740589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>794886</t>
+          <t>794433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>841746</t>
+          <t>839366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>907993</t>
+          <t>908957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1596418</t>
+          <t>1598071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1688788</t>
+          <t>1684417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89297</t>
+          <t>90925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129839</t>
+          <t>131093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77207</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178130</t>
+          <t>177406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230013</t>
+          <t>230850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1562555</t>
+          <t>1561301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1603097</t>
+          <t>1601469</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1473307</t>
+          <t>1470673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1510466</t>
+          <t>1510564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3050054</t>
+          <t>3049217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3101937</t>
+          <t>3102661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>31251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57399</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>55772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89318</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494009</t>
+          <t>492642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520467</t>
+          <t>520157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437163</t>
+          <t>435880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457865</t>
+          <t>456892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>938502</t>
+          <t>939056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972876</t>
+          <t>972048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379184</t>
+          <t>380247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449429</t>
+          <t>452546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>525033</t>
+          <t>524789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>608714</t>
+          <t>611644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>922669</t>
+          <t>915783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1040186</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2826096</t>
+          <t>2822979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2896341</t>
+          <t>2895278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2770483</t>
+          <t>2767553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2854164</t>
+          <t>2854408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5614536</t>
+          <t>5625785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5732053</t>
+          <t>5738939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309200</t>
+          <t>306889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369332</t>
+          <t>368749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>530048</t>
+          <t>531954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>608766</t>
+          <t>603894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>860139</t>
+          <t>852712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>955334</t>
+          <t>951556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>605311</t>
+          <t>605894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665443</t>
+          <t>667754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>725805</t>
+          <t>730677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>804523</t>
+          <t>802617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1353880</t>
+          <t>1357658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1449075</t>
+          <t>1456502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159541</t>
+          <t>158028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211915</t>
+          <t>212138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122226</t>
+          <t>120668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170963</t>
+          <t>169196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294638</t>
+          <t>294071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>363648</t>
+          <t>366798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1748107</t>
+          <t>1747884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1800481</t>
+          <t>1801994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1579761</t>
+          <t>1581528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1628498</t>
+          <t>1630056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3347098</t>
+          <t>3343948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3416108</t>
+          <t>3416675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33327</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61810</t>
+          <t>61299</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44106</t>
+          <t>42877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59156</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98669</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418522</t>
+          <t>419033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447005</t>
+          <t>447361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>413548</t>
+          <t>414777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437835</t>
+          <t>439346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>839317</t>
+          <t>840785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878830</t>
+          <t>879061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>523474</t>
+          <t>527370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>616607</t>
+          <t>616299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>695863</t>
+          <t>693181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>792747</t>
+          <t>792455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1245616</t>
+          <t>1249757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1375353</t>
+          <t>1376411</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2798390</t>
+          <t>2798698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2891523</t>
+          <t>2887627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2750202</t>
+          <t>2750494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2847086</t>
+          <t>2849768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5582593</t>
+          <t>5581535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5712330</t>
+          <t>5708189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208891</t>
+          <t>206935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>256024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>350389</t>
+          <t>352551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>415752</t>
+          <t>417702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>572389</t>
+          <t>575671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655657</t>
+          <t>654659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498394</t>
+          <t>498323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>545456</t>
+          <t>547412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578908</t>
+          <t>576958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>644271</t>
+          <t>642109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1093350</t>
+          <t>1094348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1176618</t>
+          <t>1173336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191947</t>
+          <t>193543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250162</t>
+          <t>249788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183819</t>
+          <t>184562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243971</t>
+          <t>244749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390290</t>
+          <t>386371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>471617</t>
+          <t>473241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1826223</t>
+          <t>1826597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1884438</t>
+          <t>1882842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1744329</t>
+          <t>1743551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1804481</t>
+          <t>1803738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3593068</t>
+          <t>3591444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3674395</t>
+          <t>3678314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66008</t>
+          <t>67330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42626</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63944</t>
+          <t>63638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101243</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480878</t>
+          <t>479556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508864</t>
+          <t>508308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506514</t>
+          <t>505015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530041</t>
+          <t>530467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994784</t>
+          <t>993884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032083</t>
+          <t>1032389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>465145</t>
+          <t>461433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548358</t>
+          <t>544056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>583162</t>
+          <t>580645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>677769</t>
+          <t>676884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1064886</t>
+          <t>1060195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1195175</t>
+          <t>1188443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2829260</t>
+          <t>2833562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2912473</t>
+          <t>2916185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2854331</t>
+          <t>2855216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2948938</t>
+          <t>2951455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5714543</t>
+          <t>5721275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5844832</t>
+          <t>5849523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>188107</t>
+          <t>203339</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169128</t>
+          <t>181374</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207006</t>
+          <t>224650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>375088</t>
+          <t>400631</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353728</t>
+          <t>378448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>396821</t>
+          <t>422400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>563194</t>
+          <t>603970</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534272</t>
+          <t>571944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594510</t>
+          <t>634186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>325835</t>
+          <t>374203</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306936</t>
+          <t>352892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344814</t>
+          <t>396168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>376974</t>
+          <t>419485</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355241</t>
+          <t>397716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398334</t>
+          <t>441668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>702810</t>
+          <t>793688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671494</t>
+          <t>763472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731732</t>
+          <t>825714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>314896</t>
+          <t>337529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>227422</t>
+          <t>308883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366552</t>
+          <t>371084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>460172</t>
+          <t>286480</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270184</t>
+          <t>260287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>949187</t>
+          <t>311093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>775067</t>
+          <t>624009</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575578</t>
+          <t>585300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1322862</t>
+          <t>668383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1974547</t>
+          <t>1892115</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1922891</t>
+          <t>1858560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2062021</t>
+          <t>1920761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1776973</t>
+          <t>1884227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1287958</t>
+          <t>1859614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1966961</t>
+          <t>1910420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3751521</t>
+          <t>3776343</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3203726</t>
+          <t>3731969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3951010</t>
+          <t>3815052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2229644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2229644</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289443</t>
+          <t>2229644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526588</t>
+          <t>4400352</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526588</t>
+          <t>4400352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526588</t>
+          <t>4400352</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108967</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>102622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127506</t>
+          <t>139822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>78443</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56113</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79856</t>
+          <t>92195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175758</t>
+          <t>198600</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154252</t>
+          <t>176270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196529</t>
+          <t>221473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>537656</t>
+          <t>591430</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519117</t>
+          <t>571765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555268</t>
+          <t>608965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>593671</t>
+          <t>656434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>580607</t>
+          <t>642682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604350</t>
+          <t>668705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1131328</t>
+          <t>1247864</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1110557</t>
+          <t>1224991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1152834</t>
+          <t>1270194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>611969</t>
+          <t>661025</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>469665</t>
+          <t>622391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>674367</t>
+          <t>706139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>902051</t>
+          <t>765554</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>720288</t>
+          <t>725561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1420887</t>
+          <t>804393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1514020</t>
+          <t>1426579</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1317410</t>
+          <t>1365839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2100399</t>
+          <t>1484748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2838040</t>
+          <t>2857748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2775642</t>
+          <t>2812634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2980344</t>
+          <t>2896382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2747619</t>
+          <t>2960147</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2228783</t>
+          <t>2921308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2929382</t>
+          <t>3000140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5585658</t>
+          <t>5817895</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4999279</t>
+          <t>5759726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5782268</t>
+          <t>5878635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450009</t>
+          <t>3518773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450009</t>
+          <t>3518773</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450009</t>
+          <t>3518773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099678</t>
+          <t>7244474</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099678</t>
+          <t>7244474</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099678</t>
+          <t>7244474</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
